--- a/docs/Decodifiche/96_dec_motivo_recupero.xlsx
+++ b/docs/Decodifiche/96_dec_motivo_recupero.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -32,37 +32,40 @@
     <t>1</t>
   </si>
   <si>
-    <t>Indisponibilita' del sistema gestionale</t>
+    <t>Indisponibilità del sistema gestionale</t>
+  </si>
+  <si>
+    <t>0001-01-01 13:59:23.0</t>
+  </si>
+  <si>
+    <t>9999-12-31 13:59:23.0</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Atto formato fuori da casa comunale</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Caso d'uso non previsto nel sistema centrale</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Indisponibilità del sistema centrale</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Inefficacia atto per duplicazione</t>
   </si>
   <si>
     <t>2000-01-01 00:00:00.0</t>
-  </si>
-  <si>
-    <t>9999-12-31 00:00:00.0</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Atto formato fuori da casa comunale</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Caso d'uso non previsto nel sistema centrale</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Indisponibilita' del sistema centrale</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Inefficacia atto per duplicazione</t>
   </si>
   <si>
     <t>1999-12-31 00:00:00.0</t>
@@ -236,30 +239,30 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
